--- a/Lab_4/data/partB/param_optimization_process/v200_k40_s100_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v200_k40_s100_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>10</v>
@@ -600,19 +600,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,16 +646,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -677,16 +677,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>9</v>
@@ -695,7 +695,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -704,19 +704,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -726,49 +726,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11</v>
+      </c>
+      <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -787,31 +787,31 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -839,37 +839,37 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -882,34 +882,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>13</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8</v>
-      </c>
       <c r="I9" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -937,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -958,25 +958,25 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -995,25 +995,25 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1059,25 +1059,25 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1090,49 +1090,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1142,49 +1142,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1209,13 +1209,13 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
         <v>2</v>
@@ -1233,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1246,49 +1246,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12742,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17774,7 +17774,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18539,7 +18539,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19610,7 +19610,7 @@
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20341,7 +20341,7 @@
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20392,7 +20392,7 @@
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21004,7 +21004,7 @@
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21582,7 +21582,7 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22126,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23214,7 @@
       </c>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="C1299" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23435,7 +23435,7 @@
       </c>
       <c r="C1302" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23979,7 +23979,7 @@
       </c>
       <c r="C1334" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25356,7 +25356,7 @@
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25849,7 +25849,7 @@
       </c>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25968,7 +25968,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26138,7 +26138,7 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26274,7 +26274,7 @@
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26716,7 +26716,7 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26784,7 +26784,7 @@
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
